--- a/Docs/Estimation Fiche de stage - ETU003350.xlsx
+++ b/Docs/Estimation Fiche de stage - ETU003350.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eccc9ba13b5ec9e0/Documents/GitHub/Gestion-de-recherche-en-Biodiversite/Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_8FCC563B61DD3984174A83705858A2E158379DE7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A6DEB6E-3F46-48B5-8AEA-53914BF00DC6}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="11_8FCC563B61DD3984174A83705858A2E158379DE7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{453521FF-AFC0-4699-96EA-61FF0D2AE7B9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Estimation Agile info 4" sheetId="6" r:id="rId1"/>
@@ -156,10 +156,10 @@
     <t>SOMME TOTAL</t>
   </si>
   <si>
-    <t>Analyse des besoins</t>
-  </si>
-  <si>
-    <t>Conception de la base de donnees</t>
+    <t>Analyse</t>
+  </si>
+  <si>
+    <t>Conception de la base de données</t>
   </si>
 </sst>
 </file>
